--- a/Outputs/Tables/DieboldMariano.xlsx
+++ b/Outputs/Tables/DieboldMariano.xlsx
@@ -6,16 +6,16 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="DM_Test" sheetId="1" r:id="rId2"/>
+    <sheet name="DM_BO" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="27" uniqueCount="22">
-  <si>
-    <t>Test de Diebold-Mariano — Comparación de poder predictivo</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="26" uniqueCount="21">
+  <si>
+    <t>Test de Diebold-Mariano — pronósticos B-O corregidos</t>
   </si>
   <si>
     <t>Comp.</t>
@@ -30,13 +30,13 @@
     <t>Media d_t</t>
   </si>
   <si>
-    <t>Estadístico DM</t>
+    <t>DM stat</t>
   </si>
   <si>
     <t>p-valor</t>
   </si>
   <si>
-    <t>Significancia</t>
+    <t>Sig.</t>
   </si>
   <si>
     <t>Conclusión</t>
@@ -72,60 +72,17 @@
     <t>C</t>
   </si>
   <si>
-    <t>Lags Newey-West: 3 | Obs. test: 36</t>
-  </si>
-  <si>
-    <t>H0: igual precisión predictiva. d_t = MSE(modelo 1) - MSE(modelo 2).</t>
-  </si>
-  <si>
-    <t>*** p&lt;0.01  ** p&lt;0.05  * p&lt;0.10</t>
+    <t>Newey-West (3 lags) | Obs. test: 36</t>
+  </si>
+  <si>
+    <t>d_t = e²_BO(M1) - e²_BO(M2). *** p&lt;0.01  ** p&lt;0.05  * p&lt;0.10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <numFmts count="2">
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
-  </numFmts>
-  <fonts count="10">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -139,7 +96,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -147,111 +104,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -261,7 +119,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -305,14 +163,14 @@
       <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1">
-        <v>-639.04064305623376</v>
-      </c>
-      <c r="E3" s="2">
-        <v>-1.3311237010300301</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0.19175460648287329</v>
+      <c r="D3">
+        <v>-594.44774585300024</v>
+      </c>
+      <c r="E3">
+        <v>-1.254965761651254</v>
+      </c>
+      <c r="F3">
+        <v>0.21780645813702049</v>
       </c>
       <c r="G3" t="s">
         <v>12</v>
@@ -331,14 +189,14 @@
       <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="4">
-        <v>-453.5807965066698</v>
-      </c>
-      <c r="E4" s="5">
-        <v>-2.4257703583126449</v>
-      </c>
-      <c r="F4" s="6">
-        <v>0.0205700885306851</v>
+      <c r="D4">
+        <v>-466.57848845587841</v>
+      </c>
+      <c r="E4">
+        <v>-2.503505832381566</v>
+      </c>
+      <c r="F4">
+        <v>0.017112008118665201</v>
       </c>
       <c r="G4" t="s">
         <v>16</v>
@@ -357,14 +215,14 @@
       <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="7">
-        <v>185.45984522501629</v>
-      </c>
-      <c r="E5" s="8">
-        <v>0.43285718395312672</v>
-      </c>
-      <c r="F5" s="9">
-        <v>0.6677743031867821</v>
+      <c r="D5">
+        <v>127.86926672193739</v>
+      </c>
+      <c r="E5">
+        <v>0.30265549961682869</v>
+      </c>
+      <c r="F5">
+        <v>0.76394390487603647</v>
       </c>
       <c r="G5" t="s">
         <v>12</v>
@@ -383,11 +241,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>